--- a/game_document/Sumeeper_Perk_Sheet.xlsx
+++ b/game_document/Sumeeper_Perk_Sheet.xlsx
@@ -91,16 +91,16 @@
     <t>Full-Counter, Guarding</t>
   </si>
   <si>
-    <t>เมื่อ Action gauge เต็มจะไม่รีเซ็ตแบบปกติ
+    <t>เมื่อ Special Gauge เต็มจะไม่รีเซ็ตแบบปกติ
 แต่จะรีเซ็ตเมื่อผู้เล่นโดนโจมตีแทน
-เมื่อรีเซ็ตจะโจมตีโต้กลับ = ATK + ATK ของศัตรู + จำนวนช่อง Action gauge</t>
+เมื่อรีเซ็ตจะโจมตีโต้กลับ = ATK + ATK ของศัตรู + จำนวนช่อง Special Gauge</t>
   </si>
   <si>
     <t>Sumeeper — Normal Perks</t>
   </si>
   <si>
-    <t>On-Damaged: Reset Action gauge.
-On-Action: Counter — deal (Player ATK + Enemy ATK + Action gauge slots) damage.</t>
+    <t>On-Damaged: Reset Special Gauge.
+On-Action: Counter — deal (Player ATK + Enemy ATK + Special Gauge slots) damage.</t>
   </si>
   <si>
     <t>การโจมตีโต้กลับทำความเสียหายเพิ่มขึ้น 50/100/150%</t>
@@ -109,12 +109,12 @@
     <t>Berserker</t>
   </si>
   <si>
-    <t>On-Action: Restore HP เท่ากับจำนวน Action gauge slot ที่ลดลงไปใน combat นี้ + 1
-ทุกครั้งที่ On-Half ทำงาน Action gauge max slots ลดลง 1 (ต่ำสุด 2)</t>
-  </si>
-  <si>
-    <t>On-Action: Restore HP equal to Action gauge slots decreased in this combat +1.
-Every On-Half: Action gauge slots − 1 (min 2).</t>
+    <t>On-Action: Restore HP เท่ากับจำนวน Special Gauge slot ที่ลดลงไปใน combat นี้ + 1
+ทุกครั้งที่ On-Half ทำงาน Special Gauge max slots ลดลง 1 (ต่ำสุด 2)</t>
+  </si>
+  <si>
+    <t>On-Action: Restore HP equal to Special Gauge slots decreased in this combat +1.
+Every On-Half: Special Gauge slots − 1 (min 2).</t>
   </si>
   <si>
     <t>Duelist</t>
@@ -150,19 +150,19 @@
     <t>Another Shot</t>
   </si>
   <si>
-    <t>ในขณะที่ Action-Gauge เต็มจะได้รับ Armor 1/2/3 ชั่วคราว</t>
-  </si>
-  <si>
-    <t>while action gauge is full gain temporary armor 1/2/3</t>
+    <t>ในขณะที่ Special Gauge เต็มจะได้รับ Armor 1/2/3 ชั่วคราว</t>
+  </si>
+  <si>
+    <t>while Special Gauge is full gain temporary armor 1/2/3</t>
   </si>
   <si>
     <t>แทนที่การโจมตี burst ปกติ
-On-Action จะทำการโจมตีเสริมจำนวนครั้งเท่ากับช่อง Action gauge
+On-Action จะทำการโจมตีเสริมจำนวนครั้งเท่ากับช่อง Special Gauge
 การโจมตีเสริมแต่ละครั้งทำความเสียหาย = 50% ของ ATK</t>
   </si>
   <si>
     <t>Replaces normal On-Action behavior.
-On-Action: bonus attacks equal to Action gauge slots, each dealing 50% ATK.</t>
+On-Action: bonus attacks equal to Special Gauge slots, each dealing 50% ATK.</t>
   </si>
   <si>
     <t>Devourer</t>
@@ -173,43 +173,43 @@
   <si>
     <t>แทนที่การโจมตี burst
 On-Action จะสุ่ม trigger Combat Ability ที่ผู้เล่นมี (On-Start, On-Hit, On-Damaged, On-Half)
-จำนวนครั้งเท่ากับช่อง Action gauge</t>
+จำนวนครั้งเท่ากับช่อง Special Gauge</t>
   </si>
   <si>
     <t>Open Pantry</t>
   </si>
   <si>
     <t>Replaces normal On-Action behavior.
-On-Action: randomly trigger player Combat Abilities x Action gauge slots times.</t>
-  </si>
-  <si>
-    <t>On-Action ผู้เล่นจะได้รับ ATK เพิ่มขึ้น = จำนวนช่อง Action gauge
+On-Action: randomly trigger player Combat Abilities x Special Gauge slots times.</t>
+  </si>
+  <si>
+    <t>On-Action ผู้เล่นจะได้รับ ATK เพิ่มขึ้น = จำนวนช่อง Special Gauge
 ATK ที่ได้จะคงอยู่ตลอด combat นี้</t>
   </si>
   <si>
-    <t>On-Action: gain ATK equal to Action gauge slots.
+    <t>On-Action: gain ATK equal to Special Gauge slots.
 Lasts until combat ends.</t>
   </si>
   <si>
     <t>แทนที่การโจมตี burst ปกติ
-On-Action จะสุ่มขโมย stat ของศัตรู 1 ชนิด (ATK/DEF/SPD) ต่อจำนวนช่อง Action gauge max slot 
+On-Action จะสุ่มขโมย stat ของศัตรู 1 ชนิด (ATK/DEF/SPD) ต่อจำนวนช่อง Special Gauge max slot 
 ผู้เล่นได้ stat เพิ่ม | ศัตรูเสีย stat เท่ากัน 
 stat คงอยู่ตลอด combat นี้</t>
   </si>
   <si>
     <t>On-Action: randomly steal one stat (ATK/DEF/SPD) from enemy.
-Amount per Action gauge max slots. Player gains, enemy loses.
+Amount per Special Gauge max slots. Player gains, enemy loses.
 Lasts until combat ends.</t>
   </si>
   <si>
     <t>On-Exposed สามารถ trigger ได้เพิ่มขึ้น 1/2/3 ครั้ง</t>
   </si>
   <si>
-    <t>ทุกครั้งที่ Action gauge ลดลง ATK จะเพิ่มขึ้น 1/2/3 คูณด้วยจำนวนครั้งที่ On-Half ทำงานใน combat นี้
+    <t>ทุกครั้งที่ Special Gauge ลดลง ATK จะเพิ่มขึ้น 1/2/3 คูณด้วยจำนวนครั้งที่ On-Half ทำงานใน combat นี้
 ATK ที่ได้คงอยู่ตลอด combat นี้</t>
   </si>
   <si>
-    <t>Every Action gauge decrease: gain ATK equal to (1/2/3 × On-Half that triggers in this combat).
+    <t>Every Special Gauge decrease: gain ATK equal to (1/2/3 × On-Half that triggers in this combat).
 Lasts until combat ends.</t>
   </si>
   <si>
@@ -246,10 +246,10 @@
     <t>Extra Burner</t>
   </si>
   <si>
-    <t>เพิ่ม Action gauge max slots อีก 1/2/3 ช่อง</t>
-  </si>
-  <si>
-    <t>+1/2/3 to Action gauge max slots.</t>
+    <t>เพิ่ม Special Gauge max slots อีก 1/2/3 ช่อง</t>
+  </si>
+  <si>
+    <t>+1/2/3 to Special Gauge max slots.</t>
   </si>
   <si>
     <t>Tenderize</t>
@@ -258,10 +258,10 @@
     <t>Full Force</t>
   </si>
   <si>
-    <t>On-Hit จะทำงานเพิ่มขึ้นตามจำนวน Action gauge max slots</t>
-  </si>
-  <si>
-    <t>On-Hit triggers additional times equal to Action gauge max slots.</t>
+    <t>On-Hit จะทำงานเพิ่มขึ้นตามจำนวน Special Gauge max slots</t>
+  </si>
+  <si>
+    <t>On-Hit triggers additional times equal to Special Gauge max slots.</t>
   </si>
   <si>
     <t>การโจมตีเสริมทำความเสียหายเพิ่มขึ้นเป็น 60/70/70% ของ ATK</t>
@@ -273,10 +273,10 @@
     <t>Bonus attacks deal damage 60/70/80% equal of ATK</t>
   </si>
   <si>
-    <t>สามารถหลบหลีกได้ โดยอัตราการหลบหลีกเพิ่มตาม Action gauge max slots ช่องละ 5/7/10%</t>
-  </si>
-  <si>
-    <t>Gain dodge chance: 5/7/10% per current Action gauge max slots.</t>
+    <t>สามารถหลบหลีกได้ โดยอัตราการหลบหลีกเพิ่มตาม Special Gauge max slots ช่องละ 5/7/10%</t>
+  </si>
+  <si>
+    <t>Gain dodge chance: 5/7/10% per current Special Gauge max slots.</t>
   </si>
   <si>
     <t>Boning Knife</t>
@@ -303,7 +303,7 @@
     <t>Restoration</t>
   </si>
   <si>
-    <t>เมื่อ Action gauge เต็มผู้เล่นจะ Restore HP 1/2/3</t>
+    <t>เมื่อ Special Gauge เต็มผู้เล่นจะ Restore HP 1/2/3</t>
   </si>
   <si>
     <t>On-Action player restores 1/2/3 HP.</t>
@@ -324,20 +324,20 @@
     <t>Each random ability trigger procs twice per activation.</t>
   </si>
   <si>
-    <t>On-Action: มีโอกาส 25/35/50% ที่ Action gauge จะไม่ reset 
+    <t>On-Action: มีโอกาส 25/35/50% ที่ Special Gauge จะไม่ reset 
 เมื่อทำงาน ATK ลดลง 1 ตลอด combat นี้</t>
   </si>
   <si>
-    <t>On-Action: 25/35/50% chance that Action gauge does not reset.
+    <t>On-Action: 25/35/50% chance that Special Gauge does not reset.
 when trigger : lose 1 ATK Lasts until combat ends.</t>
   </si>
   <si>
-    <t>เมื่อ Action gauge เต็มผู้เล่นจะขโมย Action gauge ปัจจุบันของศัตรู 1 ช่อง
-(ไม่กระทบ max Action gauge ของศัตรู)</t>
-  </si>
-  <si>
-    <t>On-Action : steal 1 current Action gauge slot from enemy.
-Does not affect enemy's max Action gauge.</t>
+    <t>เมื่อ Special Gauge เต็มผู้เล่นจะขโมย Special Gauge ปัจจุบันของศัตรู 1 ช่อง
+(ไม่กระทบ max Special Gauge ของศัตรู)</t>
+  </si>
+  <si>
+    <t>On-Action : steal 1 current Special Gauge slot from enemy.
+Does not affect enemy's max Special Gauge.</t>
   </si>
 </sst>
 </file>

--- a/game_document/Sumeeper_Perk_Sheet.xlsx
+++ b/game_document/Sumeeper_Perk_Sheet.xlsx
@@ -91,16 +91,16 @@
     <t>Full-Counter, Guarding</t>
   </si>
   <si>
-    <t>เมื่อ Special Gauge เต็มจะไม่รีเซ็ตแบบปกติ
+    <t>เมื่อ Action gauge เต็มจะไม่รีเซ็ตแบบปกติ
 แต่จะรีเซ็ตเมื่อผู้เล่นโดนโจมตีแทน
-เมื่อรีเซ็ตจะโจมตีโต้กลับ = ATK + ATK ของศัตรู + จำนวนช่อง Special Gauge</t>
+เมื่อรีเซ็ตจะโจมตีโต้กลับ = ATK + ATK ของศัตรู + จำนวนช่อง Action gauge</t>
   </si>
   <si>
     <t>Sumeeper — Normal Perks</t>
   </si>
   <si>
-    <t>On-Damaged: Reset Special Gauge.
-On-Action: Counter — deal (Player ATK + Enemy ATK + Special Gauge slots) damage.</t>
+    <t>On-Damaged: Reset Action gauge.
+On-Action: Counter — deal (Player ATK + Enemy ATK + Action gauge slots) damage.</t>
   </si>
   <si>
     <t>การโจมตีโต้กลับทำความเสียหายเพิ่มขึ้น 50/100/150%</t>
@@ -109,12 +109,12 @@
     <t>Berserker</t>
   </si>
   <si>
-    <t>On-Action: Restore HP เท่ากับจำนวน Special Gauge slot ที่ลดลงไปใน combat นี้ + 1
-ทุกครั้งที่ On-Half ทำงาน Special Gauge max slots ลดลง 1 (ต่ำสุด 2)</t>
-  </si>
-  <si>
-    <t>On-Action: Restore HP equal to Special Gauge slots decreased in this combat +1.
-Every On-Half: Special Gauge slots − 1 (min 2).</t>
+    <t>On-Action: Restore HP เท่ากับจำนวน Action gauge slot ที่ลดลงไปใน combat นี้ + 1
+ทุกครั้งที่ On-Half ทำงาน Action gauge max slots ลดลง 1 (ต่ำสุด 2)</t>
+  </si>
+  <si>
+    <t>On-Action: Restore HP equal to Action gauge slots decreased in this combat +1.
+Every On-Half: Action gauge slots − 1 (min 2).</t>
   </si>
   <si>
     <t>Duelist</t>
@@ -150,19 +150,19 @@
     <t>Another Shot</t>
   </si>
   <si>
-    <t>ในขณะที่ Special Gauge เต็มจะได้รับ Armor 1/2/3 ชั่วคราว</t>
-  </si>
-  <si>
-    <t>while Special Gauge is full gain temporary armor 1/2/3</t>
+    <t>ในขณะที่ Action-Gauge เต็มจะได้รับ Armor 1/2/3 ชั่วคราว</t>
+  </si>
+  <si>
+    <t>while action gauge is full gain temporary armor 1/2/3</t>
   </si>
   <si>
     <t>แทนที่การโจมตี burst ปกติ
-On-Action จะทำการโจมตีเสริมจำนวนครั้งเท่ากับช่อง Special Gauge
+On-Action จะทำการโจมตีเสริมจำนวนครั้งเท่ากับช่อง Action gauge
 การโจมตีเสริมแต่ละครั้งทำความเสียหาย = 50% ของ ATK</t>
   </si>
   <si>
     <t>Replaces normal On-Action behavior.
-On-Action: bonus attacks equal to Special Gauge slots, each dealing 50% ATK.</t>
+On-Action: bonus attacks equal to Action gauge slots, each dealing 50% ATK.</t>
   </si>
   <si>
     <t>Devourer</t>
@@ -173,43 +173,43 @@
   <si>
     <t>แทนที่การโจมตี burst
 On-Action จะสุ่ม trigger Combat Ability ที่ผู้เล่นมี (On-Start, On-Hit, On-Damaged, On-Half)
-จำนวนครั้งเท่ากับช่อง Special Gauge</t>
+จำนวนครั้งเท่ากับช่อง Action gauge</t>
   </si>
   <si>
     <t>Open Pantry</t>
   </si>
   <si>
     <t>Replaces normal On-Action behavior.
-On-Action: randomly trigger player Combat Abilities x Special Gauge slots times.</t>
-  </si>
-  <si>
-    <t>On-Action ผู้เล่นจะได้รับ ATK เพิ่มขึ้น = จำนวนช่อง Special Gauge
+On-Action: randomly trigger player Combat Abilities x Action gauge slots times.</t>
+  </si>
+  <si>
+    <t>On-Action ผู้เล่นจะได้รับ ATK เพิ่มขึ้น = จำนวนช่อง Action gauge
 ATK ที่ได้จะคงอยู่ตลอด combat นี้</t>
   </si>
   <si>
-    <t>On-Action: gain ATK equal to Special Gauge slots.
+    <t>On-Action: gain ATK equal to Action gauge slots.
 Lasts until combat ends.</t>
   </si>
   <si>
     <t>แทนที่การโจมตี burst ปกติ
-On-Action จะสุ่มขโมย stat ของศัตรู 1 ชนิด (ATK/DEF/SPD) ต่อจำนวนช่อง Special Gauge max slot 
+On-Action จะสุ่มขโมย stat ของศัตรู 1 ชนิด (ATK/DEF/SPD) ต่อจำนวนช่อง Action gauge max slot 
 ผู้เล่นได้ stat เพิ่ม | ศัตรูเสีย stat เท่ากัน 
 stat คงอยู่ตลอด combat นี้</t>
   </si>
   <si>
     <t>On-Action: randomly steal one stat (ATK/DEF/SPD) from enemy.
-Amount per Special Gauge max slots. Player gains, enemy loses.
+Amount per Action gauge max slots. Player gains, enemy loses.
 Lasts until combat ends.</t>
   </si>
   <si>
     <t>On-Exposed สามารถ trigger ได้เพิ่มขึ้น 1/2/3 ครั้ง</t>
   </si>
   <si>
-    <t>ทุกครั้งที่ Special Gauge ลดลง ATK จะเพิ่มขึ้น 1/2/3 คูณด้วยจำนวนครั้งที่ On-Half ทำงานใน combat นี้
+    <t>ทุกครั้งที่ Action gauge ลดลง ATK จะเพิ่มขึ้น 1/2/3 คูณด้วยจำนวนครั้งที่ On-Half ทำงานใน combat นี้
 ATK ที่ได้คงอยู่ตลอด combat นี้</t>
   </si>
   <si>
-    <t>Every Special Gauge decrease: gain ATK equal to (1/2/3 × On-Half that triggers in this combat).
+    <t>Every Action gauge decrease: gain ATK equal to (1/2/3 × On-Half that triggers in this combat).
 Lasts until combat ends.</t>
   </si>
   <si>
@@ -246,10 +246,10 @@
     <t>Extra Burner</t>
   </si>
   <si>
-    <t>เพิ่ม Special Gauge max slots อีก 1/2/3 ช่อง</t>
-  </si>
-  <si>
-    <t>+1/2/3 to Special Gauge max slots.</t>
+    <t>เพิ่ม Action gauge max slots อีก 1/2/3 ช่อง</t>
+  </si>
+  <si>
+    <t>+1/2/3 to Action gauge max slots.</t>
   </si>
   <si>
     <t>Tenderize</t>
@@ -258,10 +258,10 @@
     <t>Full Force</t>
   </si>
   <si>
-    <t>On-Hit จะทำงานเพิ่มขึ้นตามจำนวน Special Gauge max slots</t>
-  </si>
-  <si>
-    <t>On-Hit triggers additional times equal to Special Gauge max slots.</t>
+    <t>On-Hit จะทำงานเพิ่มขึ้นตามจำนวน Action gauge max slots</t>
+  </si>
+  <si>
+    <t>On-Hit triggers additional times equal to Action gauge max slots.</t>
   </si>
   <si>
     <t>การโจมตีเสริมทำความเสียหายเพิ่มขึ้นเป็น 60/70/70% ของ ATK</t>
@@ -273,10 +273,10 @@
     <t>Bonus attacks deal damage 60/70/80% equal of ATK</t>
   </si>
   <si>
-    <t>สามารถหลบหลีกได้ โดยอัตราการหลบหลีกเพิ่มตาม Special Gauge max slots ช่องละ 5/7/10%</t>
-  </si>
-  <si>
-    <t>Gain dodge chance: 5/7/10% per current Special Gauge max slots.</t>
+    <t>สามารถหลบหลีกได้ โดยอัตราการหลบหลีกเพิ่มตาม Action gauge max slots ช่องละ 5/7/10%</t>
+  </si>
+  <si>
+    <t>Gain dodge chance: 5/7/10% per current Action gauge max slots.</t>
   </si>
   <si>
     <t>Boning Knife</t>
@@ -303,7 +303,7 @@
     <t>Restoration</t>
   </si>
   <si>
-    <t>เมื่อ Special Gauge เต็มผู้เล่นจะ Restore HP 1/2/3</t>
+    <t>เมื่อ Action gauge เต็มผู้เล่นจะ Restore HP 1/2/3</t>
   </si>
   <si>
     <t>On-Action player restores 1/2/3 HP.</t>
@@ -324,20 +324,20 @@
     <t>Each random ability trigger procs twice per activation.</t>
   </si>
   <si>
-    <t>On-Action: มีโอกาส 25/35/50% ที่ Special Gauge จะไม่ reset 
+    <t>On-Action: มีโอกาส 25/35/50% ที่ Action gauge จะไม่ reset 
 เมื่อทำงาน ATK ลดลง 1 ตลอด combat นี้</t>
   </si>
   <si>
-    <t>On-Action: 25/35/50% chance that Special Gauge does not reset.
+    <t>On-Action: 25/35/50% chance that Action gauge does not reset.
 when trigger : lose 1 ATK Lasts until combat ends.</t>
   </si>
   <si>
-    <t>เมื่อ Special Gauge เต็มผู้เล่นจะขโมย Special Gauge ปัจจุบันของศัตรู 1 ช่อง
-(ไม่กระทบ max Special Gauge ของศัตรู)</t>
-  </si>
-  <si>
-    <t>On-Action : steal 1 current Special Gauge slot from enemy.
-Does not affect enemy's max Special Gauge.</t>
+    <t>เมื่อ Action gauge เต็มผู้เล่นจะขโมย Action gauge ปัจจุบันของศัตรู 1 ช่อง
+(ไม่กระทบ max Action gauge ของศัตรู)</t>
+  </si>
+  <si>
+    <t>On-Action : steal 1 current Action gauge slot from enemy.
+Does not affect enemy's max Action gauge.</t>
   </si>
 </sst>
 </file>
